--- a/artfynd/A 933-2023 artfynd.xlsx
+++ b/artfynd/A 933-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 933-2023 artfynd.xlsx
+++ b/artfynd/A 933-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94540583</v>
+        <v>94540743</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,36 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534227.1411305455</v>
+        <v>534233</v>
       </c>
       <c r="R2" t="n">
-        <v>7009746.702217132</v>
+        <v>7009736</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,19 +744,9 @@
           <t>2021-06-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,52 +773,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94540558</v>
+        <v>94539441</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534238.1547663109</v>
+        <v>534207</v>
       </c>
       <c r="R3" t="n">
-        <v>7009772.981685773</v>
+        <v>7009784</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2021-06-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,52 +873,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94540747</v>
+        <v>94540697</v>
       </c>
       <c r="B4" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534233.5694741313</v>
+        <v>534242</v>
       </c>
       <c r="R4" t="n">
-        <v>7009736.84659842</v>
+        <v>7009745</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,19 +944,9 @@
           <t>2021-06-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,52 +973,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94540600</v>
+        <v>94540728</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41670</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534226.3430815388</v>
+        <v>534245</v>
       </c>
       <c r="R5" t="n">
-        <v>7009736.769941991</v>
+        <v>7009727</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1092,19 +1044,9 @@
           <t>2021-06-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,15 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94540514</v>
+        <v>94540541</v>
       </c>
       <c r="B6" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221141</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534249.1857201515</v>
+        <v>534247</v>
       </c>
       <c r="R6" t="n">
-        <v>7009755.055578936</v>
+        <v>7009738</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1206,19 +1143,9 @@
           <t>2021-06-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,12 +1175,7 @@
         <v>94540510</v>
       </c>
       <c r="B7" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534249.1857201515</v>
+        <v>534250</v>
       </c>
       <c r="R7" t="n">
-        <v>7009755.055578936</v>
+        <v>7009755</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,19 +1242,9 @@
           <t>2021-06-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,15 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94540538</v>
+        <v>94540514</v>
       </c>
       <c r="B8" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,16 +1282,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>221141</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1401,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534246.2060873592</v>
+        <v>534250</v>
       </c>
       <c r="R8" t="n">
-        <v>7009737.882850417</v>
+        <v>7009755</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1434,19 +1341,9 @@
           <t>2021-06-28</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,15 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>94540701</v>
+        <v>94540487</v>
       </c>
       <c r="B9" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1515,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534242.0646639537</v>
+        <v>534255</v>
       </c>
       <c r="R9" t="n">
-        <v>7009745.056218711</v>
+        <v>7009802</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1548,19 +1440,9 @@
           <t>2021-06-28</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,15 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>94540541</v>
+        <v>94540538</v>
       </c>
       <c r="B10" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1603,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1629,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534246.2060873592</v>
+        <v>534247</v>
       </c>
       <c r="R10" t="n">
-        <v>7009737.882850417</v>
+        <v>7009738</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1662,19 +1539,9 @@
           <t>2021-06-28</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,15 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94540743</v>
+        <v>94540558</v>
       </c>
       <c r="B11" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,35 +1579,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>222771</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534233.5694741313</v>
+        <v>534238</v>
       </c>
       <c r="R11" t="n">
-        <v>7009736.84659842</v>
+        <v>7009773</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1775,19 +1638,9 @@
           <t>2021-06-28</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,53 +1667,47 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>94540697</v>
+        <v>94540583</v>
       </c>
       <c r="B12" t="n">
-        <v>40972</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100453</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534242.0646639537</v>
+        <v>534227</v>
       </c>
       <c r="R12" t="n">
-        <v>7009745.056218711</v>
+        <v>7009747</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,19 +1737,9 @@
           <t>2021-06-28</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,53 +1766,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>94539441</v>
+        <v>94540600</v>
       </c>
       <c r="B13" t="n">
-        <v>40972</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100453</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534207.7798315661</v>
+        <v>534227</v>
       </c>
       <c r="R13" t="n">
-        <v>7009783.485386407</v>
+        <v>7009736</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2005,19 +1836,9 @@
           <t>2021-06-28</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,53 +1865,47 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>94540728</v>
+        <v>94540701</v>
       </c>
       <c r="B14" t="n">
-        <v>40972</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100453</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534244.5047928544</v>
+        <v>534242</v>
       </c>
       <c r="R14" t="n">
-        <v>7009727.940956495</v>
+        <v>7009745</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2120,19 +1935,9 @@
           <t>2021-06-28</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,6 +1961,401 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>94540747</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ragunda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>534233</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7009736</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-06-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-06-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>94540865</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ragunda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>534272</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7009713</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-06-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-06-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>94540886</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ragunda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>534267</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7009778</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-06-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-06-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>110326978</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mörtsjöbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>534236</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7009797</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-06-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-06-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 933-2023 artfynd.xlsx
+++ b/artfynd/A 933-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94540743</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94539441</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -970,6 +985,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94540697</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94540728</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94540541</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94540510</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94540514</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94540487</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94540538</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1664,6 +1714,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94540558</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1763,6 +1818,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94540583</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1862,6 +1922,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94540600</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1961,6 +2026,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94540701</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2060,6 +2130,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94540747</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2159,6 +2234,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94540865</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2258,6 +2338,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94540886</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2356,8 +2441,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110326978</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>